--- a/Design/Excel/GameHot/Datas/Buqi/BuqiTrainer.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiTrainer.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiTrainer" sheetId="1" r:id="Rf3df535491ba4a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiTrainer" sheetId="1" r:id="R6b116884ecce4738"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -321,7 +321,7 @@
         <x:v>trainer-wind</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>踏风教习·简行</x:v>
+        <x:v>加速训练师 · 简行</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>Buqi.Content.Trainer.trainer_wind.Name</x:v>
@@ -345,7 +345,7 @@
         <x:v>trainer-ward</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>垒山教习·岳定</x:v>
+        <x:v>护盾训练师 · 岳定</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>Buqi.Content.Trainer.trainer_ward.Name</x:v>
@@ -369,7 +369,7 @@
         <x:v>trainer-pulse</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>归脉教习·苏衡</x:v>
+        <x:v>恢复训练师 · 苏衡</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>Buqi.Content.Trainer.trainer_pulse.Name</x:v>
@@ -393,7 +393,7 @@
         <x:v>trainer-craft</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>百工教习·鲁知微</x:v>
+        <x:v>强化训练师 · 鲁知微</x:v>
       </x:c>
       <x:c r="D7" t="str">
         <x:v>Buqi.Content.Trainer.trainer_craft.Name</x:v>
